--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gÃ©nÃ©ral</t>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: he didn't care whether Her Majestyâ€™s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29,1894.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29,1894.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L155: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "0 C1" vs "" :: 0</t>
@@ -646,7 +650,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L1070: line starts with digit/letter garbage token | suspicious token(s): 2From (letter/digit mix) :: 2From $1.00 to $2.50.</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • done in the first instance, repairs will</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>923</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: called " orderâ€� Mr. Hardie refused to</t>
+          <t>L514: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: worth. Ottilie Palm ， Jenetta McNeilly,</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wentworth School â€” Girls : Maggie</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • done in the first instance, repairs will</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -735,7 +739,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Works. It is stipulated that the stone</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr">
@@ -787,12 +795,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: gullible â€œheirsâ€� spent '$ 7, 600 good</t>
+          <t>L517: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: sign: John M. Byrens, Grave Bull ， Robt.</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Boysâ€™ Home- W. Hartzmark.</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Works. It is stipulated that the stone</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -818,7 +826,11 @@
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L1070: line starts with digit/letter garbage token | suspicious token(s): 2From (letter/digit mix) :: 2From $1.00 to $2.50.</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr">
@@ -838,12 +850,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -870,19 +882,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L425: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œheirs "</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: am ， Dora Trigge, Nellie. Ma-</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: architectureâ€”John M. Byrens.</t>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • up the system.</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L277: isolated marker/symbol line :: Ï‰</t>
+          <t>L277: isolated marker/symbol line :: ω</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -901,12 +913,16 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • up the system.</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr">
         <is>
-          <t>L816: abbreviation/spacing may be garbled :: enbyï¼ŒChas.F.A.Locke, Norma Luxton,</t>
+          <t>L816: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | abbreviation/spacing may be garbled :: enby，Chas.F.A.Locke, Norma Luxton,</t>
         </is>
       </c>
       <c r="W5" s="1" t="inlineStr"/>
@@ -953,14 +969,10 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L432: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: These â€œfakes " are so common and so</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Extra Advanced Course â€” Painting oil</t>
-        </is>
-      </c>
+          <t>L531: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: struction: John M. I. Byrens ， Nellie Wey.</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -1036,14 +1048,10 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Extra Advanced Course - â€” Painting oil</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mechanical Art Courseâ€”Industrial de-</t>
-        </is>
-      </c>
+          <t>L534: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): JenettaMeNefiyOttilieE (odd internal casing) :: JenettaMeNefiyOttilieE. Palm ， Dora</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1053,7 +1061,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L665: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1111,14 +1119,10 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Advanced Art Course â€” Shading from,</t>
-        </is>
-      </c>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Mitchell ， Frank Hl. Nairn ， Ottilie,</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1173,19 +1177,15 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladiesâ€™ Cotton Drawers 15c, worth 506.</t>
+          <t>L351: suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladies’ Cotton Drawers 15c, worth 506.</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L699: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L319: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " It canâ€™t be true," she said, "that</t>
-        </is>
-      </c>
+          <t>L698: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1243,17 +1243,17 @@
           <t>L353: punctuation artifact: repeated periods | suspicious token(s): 5c (letter/digit mix) :: Children's Vests, all sizes, 5c..</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladiesâ€™ Cotton Drawers 15c, worth 506.</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>L699: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L573: isolated marker/symbol line :: 25</t>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1306,17 +1306,17 @@
           <t>L355: suspicious token(s): 10c (letter/digit mix), 25c (letter/digit mix) :: Children's Vests, fine, 10c, worth 25c.</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Pursesâ€”a large purchase of fine new goods.</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>L757: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: 0</t>
+          <t>L573: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1369,17 +1369,17 @@
           <t>L357: suspicious token(s): 15c (letter/digit mix), 35c (letter/digit mix) :: Lamp Shade Laces 15c, worth 35c.</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . old question of taxationâ€”whether</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>L816: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | abbreviation/spacing may be garbled :: enby，Chas.F.A.Locke, Norma Luxton,</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: s;</t>
+          <t>L628: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1428,17 +1428,17 @@
           <t>L359: suspicious token(s): 1c (letter/digit mix) :: Ladies' Colored Linen Collars 1c.</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Fosterâ€™s latest tariff bill, and it will be</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>L834: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: bell. Matthew Garvin，Herbert Mason,</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L688: isolated marker/symbol line :: 2</t>
+          <t>L687: isolated marker/symbol line :: s;</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1487,17 +1487,17 @@
           <t>L361: suspicious token(s): 15c (letter/digit mix) :: Children's Pure Rubber Bibs 15c.</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>L839: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: vin. Fannie Gunn, Muriel Hills ； Mabel</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L689: isolated marker/symbol line :: D</t>
+          <t>L688: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1546,17 +1546,17 @@
           <t>L369: suspicious token(s): 6c (letter/digit mix) :: Ladies' Handkerchiefs, fine new lot, from 6c;</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rontoâ€™s asphalt pavement, which he</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>L860: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: shoes ，</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L689: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1606,16 +1606,12 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ done in the first instance, repairs will</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L699: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L698: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1656,7 +1652,7 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>L534: suspicious token(s): JenettaMeNefiyOttilieE (odd internal casing) :: JenettaMeNefiyOttilieE. Palm ï¼Œ Dora</t>
+          <t>L534: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): JenettaMeNefiyOttilieE (odd internal casing) :: JenettaMeNefiyOttilieE. Palm ， Dora</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
@@ -1665,16 +1661,12 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Poem read at Miss Willardâ€™s welcome</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L700: isolated marker/symbol line :: 0</t>
+          <t>L699: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1712,16 +1704,12 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Thereâ€™s but one sphere for man and</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L724: isolated marker/symbol line :: 1</t>
+          <t>L700: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1759,16 +1747,12 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: To Hades heâ€™ll be soon remanded.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L798: isolated marker/symbol line :: 3</t>
+          <t>L724: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1806,16 +1790,12 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L840: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And thatâ€™s the case with all his minions:</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L807: isolated marker/symbol line :: +</t>
+          <t>L757: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1853,16 +1833,12 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: From dirty politics": theyâ€™ve wielded</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L901: isolated marker/symbol line :: 0</t>
+          <t>L798: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1900,16 +1876,12 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: When, in a hencoopâ€™s safe dominions,</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L915: isolated marker/symbol line :: D.</t>
+          <t>L807: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1947,16 +1919,12 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L852: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Iâ€™ve not observed the uncaged bird</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L930: isolated marker/symbol line :: &lt; 3</t>
+          <t>L901: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1994,16 +1962,12 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: In government, and-thereâ€™s the rub!</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L931: isolated marker/symbol line :: N</t>
+          <t>L915: isolated marker/symbol line :: D.</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2032,7 +1996,7 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>L593: suspicious token(s): 8c (letter/digit mix) :: regular 8c, Saturday 5 Â½ c</t>
+          <t>L593: suspicious token(s): 8c (letter/digit mix) :: regular 8c, Saturday 5 ½ c</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -2041,16 +2005,12 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L867: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The very halls of state theyâ€™ll scrub,</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L933: isolated marker/symbol line :: -</t>
+          <t>L930: isolated marker/symbol line :: &lt; 3</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2079,7 +2039,7 @@
       <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>L600: suspicious token(s): 35c (letter/digit mix) :: 35c, Saturday's price 19Â½C.</t>
+          <t>L600: suspicious token(s): 35c (letter/digit mix) :: 35c, Saturday's price 19½C.</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
@@ -2088,16 +2048,12 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L880: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And when theyâ€™ve tried it, fact discloses</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L934: isolated marker/symbol line :: N</t>
+          <t>L931: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2135,16 +2091,12 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: That even election dayâ€™s serene.</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L935: isolated marker/symbol line :: G</t>
+          <t>L933: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2182,16 +2134,12 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At freedomâ€™s fount, till, newly fledged,</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L936: isolated marker/symbol line :: S</t>
+          <t>L934: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2229,16 +2177,12 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: And yetâ€”this woman cannot vote !</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L951: isolated marker/symbol line :: ,</t>
+          <t>L935: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2276,14 +2220,14 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Works. It is stipulated that the stone</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>L936: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
           <t>L1085: isolated marker/symbol line :: S</t>
@@ -2319,14 +2263,14 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Get Mowatâ€™s majority down as fine as</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>L951: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
           <t>L1168: isolated marker/symbol line :: %</t>
@@ -2362,11 +2306,7 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L1061: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: for the Governorship. If Mr. Singerlyâ€™s</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
@@ -2396,7 +2336,7 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>L887: suspicious token(s): 25c (letter/digit mix) :: 23 and 25c, Saturday 12Â½c.</t>
+          <t>L887: suspicious token(s): 25c (letter/digit mix) :: 23 and 25c, Saturday 12½c.</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -2405,11 +2345,7 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L1087: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Whatâ€™s this we see? Sir John Thomp-</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
@@ -2444,11 +2380,7 @@
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L1108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ning shoes at Kingsleyâ€™s, Nos. 26 and 28</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
@@ -2483,11 +2415,7 @@
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L1154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Are you savinâ€™ up for the Fourth of</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
@@ -2522,11 +2450,7 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L1160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Iâ€™ll have 25 cents."</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
@@ -2557,11 +2481,7 @@
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L1208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ up the system.</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr"/>
